--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_144_R15.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_144_R15.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.5597</v>
+        <v>4.273</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3121</v>
+        <v>5.9583</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.7524</v>
+        <v>-1.6852</v>
       </c>
       <c r="G2" t="n">
         <v>1.8548</v>
@@ -610,13 +610,13 @@
         <v>1.8556</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0606</v>
+        <v>-0.226</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2715</v>
+        <v>-0.0824</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2109</v>
+        <v>-0.1436</v>
       </c>
       <c r="V2" t="n">
         <v>0.7886</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>4.3917</v>
+        <v>2.5126</v>
       </c>
       <c r="E3" t="n">
-        <v>3.934</v>
+        <v>2.3573</v>
       </c>
       <c r="F3" t="n">
-        <v>0.4578</v>
+        <v>0.1553</v>
       </c>
       <c r="G3" t="n">
         <v>-0.1387</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>2.4403</v>
+        <v>0.5612</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5479</v>
+        <v>0.9713000000000001</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.1076</v>
+        <v>-0.4101</v>
       </c>
       <c r="V3" t="n">
         <v>0.9304</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. MORGAN</t>
+          <t>N. HIFI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.5083</v>
+        <v>2.0503</v>
       </c>
       <c r="E4" t="n">
-        <v>2.7332</v>
+        <v>4.6104</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2249</v>
+        <v>-2.5601</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.8042</v>
+        <v>1.4275</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.6938</v>
+        <v>-0.7504999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1104</v>
+        <v>2.178</v>
       </c>
       <c r="J4" t="n">
-        <v>2.9098</v>
+        <v>5.4884</v>
       </c>
       <c r="K4" t="n">
-        <v>1.2303</v>
+        <v>1.6776</v>
       </c>
       <c r="L4" t="n">
-        <v>1.6796</v>
+        <v>3.8108</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.714</v>
+        <v>-4.0609</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.924</v>
+        <v>-2.4282</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.79</v>
+        <v>-1.6327</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0876</v>
+        <v>-1.1598</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-3.4793</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0876</v>
+        <v>2.3195</v>
       </c>
       <c r="S4" t="n">
-        <v>0.2249</v>
+        <v>0.0325</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.1766</v>
+        <v>0.1733</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4015</v>
+        <v>-0.1408</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.7501</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.428</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.6778999999999999</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. ROBINSON</t>
+          <t>J. MORGAN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9533</v>
+        <v>1.8024</v>
       </c>
       <c r="E5" t="n">
-        <v>1.781</v>
+        <v>3.1618</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.8278</v>
+        <v>-1.3594</v>
       </c>
       <c r="G5" t="n">
-        <v>2.8537</v>
+        <v>-0.8042</v>
       </c>
       <c r="H5" t="n">
-        <v>0.7825</v>
+        <v>-0.6938</v>
       </c>
       <c r="I5" t="n">
-        <v>2.0711</v>
+        <v>-0.1104</v>
       </c>
       <c r="J5" t="n">
-        <v>3.3008</v>
+        <v>2.9098</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0692</v>
+        <v>1.2303</v>
       </c>
       <c r="L5" t="n">
-        <v>2.2317</v>
+        <v>1.6796</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.4472</v>
+        <v>-3.714</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.2866</v>
+        <v>-1.924</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1605</v>
+        <v>-1.79</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.232</v>
+        <v>2.0876</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.9278</v>
+        <v>2.0876</v>
       </c>
       <c r="S5" t="n">
-        <v>-1.6685</v>
+        <v>0.519</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8962</v>
+        <v>0.2519</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.7723</v>
+        <v>0.2671</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5361</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>N. HIFI</t>
+          <t>J. ROBINSON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8804999999999999</v>
+        <v>1.7686</v>
       </c>
       <c r="E6" t="n">
-        <v>3.4742</v>
+        <v>2.3275</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.5937</v>
+        <v>-0.5589</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4275</v>
+        <v>2.8537</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7504999999999999</v>
+        <v>0.7825</v>
       </c>
       <c r="I6" t="n">
-        <v>2.178</v>
+        <v>2.0711</v>
       </c>
       <c r="J6" t="n">
-        <v>5.4884</v>
+        <v>3.3008</v>
       </c>
       <c r="K6" t="n">
-        <v>1.6776</v>
+        <v>1.0692</v>
       </c>
       <c r="L6" t="n">
-        <v>3.8108</v>
+        <v>2.2317</v>
       </c>
       <c r="M6" t="n">
-        <v>-4.0609</v>
+        <v>-0.4472</v>
       </c>
       <c r="N6" t="n">
-        <v>-2.4282</v>
+        <v>-0.2866</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6327</v>
+        <v>-0.1605</v>
       </c>
       <c r="P6" t="n">
+        <v>-0.232</v>
+      </c>
+      <c r="Q6" t="n">
         <v>-1.1598</v>
       </c>
-      <c r="Q6" t="n">
-        <v>-3.4793</v>
-      </c>
       <c r="R6" t="n">
-        <v>2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.1373</v>
+        <v>-0.8531</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.963</v>
+        <v>-0.3497</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.1744</v>
+        <v>-0.5034</v>
       </c>
       <c r="V6" t="n">
-        <v>1.7501</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>2.428</v>
+        <v>0.5361</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.6778999999999999</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.4084</v>
+        <v>1.1722</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.8551</v>
+        <v>0.3558</v>
       </c>
       <c r="F7" t="n">
-        <v>0.4466</v>
+        <v>0.8163</v>
       </c>
       <c r="G7" t="n">
         <v>-0.521</v>
@@ -1000,13 +1000,13 @@
         <v>2.3195</v>
       </c>
       <c r="S7" t="n">
-        <v>-2.0651</v>
+        <v>-0.4845</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.9709</v>
+        <v>0.2401</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.0943</v>
+        <v>-0.7246</v>
       </c>
       <c r="V7" t="n">
         <v>-0.1418</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8258</v>
+        <v>-1.1044</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.294</v>
+        <v>-0.3372</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.5319</v>
+        <v>-0.7671</v>
       </c>
       <c r="G8" t="n">
         <v>-1.2231</v>
@@ -1078,13 +1078,13 @@
         <v>0.9278</v>
       </c>
       <c r="S8" t="n">
-        <v>0.771</v>
+        <v>0.4925</v>
       </c>
       <c r="T8" t="n">
-        <v>0.6018</v>
+        <v>0.5586</v>
       </c>
       <c r="U8" t="n">
-        <v>0.1691</v>
+        <v>-0.06610000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-0.1418</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. HOMMES</t>
+          <t>S. HERRERA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.8293</v>
+        <v>-1.3251</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7422</v>
+        <v>-1.3425</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.5716</v>
+        <v>0.0174</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2219</v>
+        <v>-2.4474</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4791</v>
+        <v>-0.2724</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7428</v>
+        <v>-2.175</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4786</v>
+        <v>-2.0218</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0504</v>
+        <v>-0.1646</v>
       </c>
       <c r="L9" t="n">
-        <v>0.4282</v>
+        <v>-1.8572</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7432</v>
+        <v>-0.4256</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4287</v>
+        <v>-0.1078</v>
       </c>
       <c r="O9" t="n">
-        <v>0.3145</v>
+        <v>-0.3178</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="S9" t="n">
-        <v>0.449</v>
+        <v>-0.6458</v>
       </c>
       <c r="T9" t="n">
-        <v>0.2636</v>
+        <v>-0.393</v>
       </c>
       <c r="U9" t="n">
-        <v>0.1854</v>
+        <v>-0.2528</v>
       </c>
       <c r="V9" t="n">
-        <v>-2.9641</v>
+        <v>1.0722</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.9641</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>S. HERRERA</t>
+          <t>D. HOMMES</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8545</v>
+        <v>-1.3609</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.7711</v>
+        <v>0.3451</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0834</v>
+        <v>-1.706</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.4474</v>
+        <v>1.2219</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.2724</v>
+        <v>0.4791</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.175</v>
+        <v>0.7428</v>
       </c>
       <c r="J10" t="n">
-        <v>-2.0218</v>
+        <v>0.4786</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1646</v>
+        <v>0.0504</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.8572</v>
+        <v>0.4282</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.4256</v>
+        <v>0.7432</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.1078</v>
+        <v>0.4287</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.3178</v>
+        <v>0.3145</v>
       </c>
       <c r="P10" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.1751</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.8215</v>
+        <v>-0.1336</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.3536</v>
+        <v>0.051</v>
       </c>
       <c r="V10" t="n">
-        <v>1.0722</v>
+        <v>-2.9641</v>
       </c>
       <c r="W10" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-2.9641</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9614</v>
+        <v>-5.2507</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3659</v>
+        <v>-1.3528</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.5955</v>
+        <v>-3.898</v>
       </c>
       <c r="G11" t="n">
         <v>-4.3194</v>
@@ -1312,13 +1312,13 @@
         <v>0.4639</v>
       </c>
       <c r="S11" t="n">
-        <v>1.9843</v>
+        <v>0.695</v>
       </c>
       <c r="T11" t="n">
-        <v>1.2467</v>
+        <v>0.2598</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7376</v>
+        <v>0.4351</v>
       </c>
       <c r="V11" t="n">
         <v>-0.9304</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-7.4127</v>
+        <v>-6.79</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.4941</v>
+        <v>-3.1402</v>
       </c>
       <c r="F12" t="n">
-        <v>-3.9186</v>
+        <v>-3.6498</v>
       </c>
       <c r="G12" t="n">
         <v>-5.0746</v>
@@ -1390,13 +1390,13 @@
         <v>0.6959</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.3381</v>
+        <v>-0.7154</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.963</v>
+        <v>-0.6091</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3752</v>
+        <v>-0.1063</v>
       </c>
       <c r="V12" t="n">
         <v>-0.5361</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.998599999999999</v>
+        <v>-2.252000000000002</v>
       </c>
       <c r="E13" t="n">
-        <v>12.1965</v>
+        <v>12.9435</v>
       </c>
       <c r="F13" t="n">
-        <v>-15.1954</v>
+        <v>-15.1955</v>
       </c>
       <c r="G13" t="n">
         <v>-7.170500000000001</v>
@@ -1444,7 +1444,7 @@
         <v>14.4755</v>
       </c>
       <c r="K13" t="n">
-        <v>2.866300000000001</v>
+        <v>2.8663</v>
       </c>
       <c r="L13" t="n">
         <v>11.6093</v>
@@ -1456,7 +1456,7 @@
         <v>-11.8934</v>
       </c>
       <c r="O13" t="n">
-        <v>-9.752700000000001</v>
+        <v>-9.752699999999999</v>
       </c>
       <c r="P13" t="n">
         <v>5.7987</v>
@@ -1468,19 +1468,19 @@
         <v>15.0769</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.454</v>
+        <v>-0.7071999999999999</v>
       </c>
       <c r="T13" t="n">
-        <v>0.1403</v>
+        <v>0.8872000000000002</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.5947</v>
+        <v>-1.5945</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.1729000000000002</v>
+        <v>-0.1729000000000004</v>
       </c>
       <c r="W13" t="n">
-        <v>6.858600000000001</v>
+        <v>6.8586</v>
       </c>
       <c r="X13" t="n">
         <v>-7.0315</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.8575</v>
+        <v>4.6659</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5656</v>
+        <v>4.9143</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7081</v>
+        <v>-0.2484</v>
       </c>
       <c r="G14" t="n">
         <v>3.1705</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>1.4756</v>
+        <v>0.284</v>
       </c>
       <c r="T14" t="n">
-        <v>2.1077</v>
+        <v>0.4564</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.6321</v>
+        <v>-0.1724</v>
       </c>
       <c r="V14" t="n">
         <v>0.2836</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. TUBELIS</t>
+          <t>N. WILLIAMS-GOSS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.4623</v>
+        <v>4.5762</v>
       </c>
       <c r="E15" t="n">
-        <v>3.3693</v>
+        <v>5.5733</v>
       </c>
       <c r="F15" t="n">
-        <v>0.093</v>
+        <v>-0.9971</v>
       </c>
       <c r="G15" t="n">
-        <v>3.4784</v>
+        <v>3.5352</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9291</v>
+        <v>4.3081</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5493</v>
+        <v>-0.7729</v>
       </c>
       <c r="J15" t="n">
-        <v>5.6018</v>
+        <v>5.6474</v>
       </c>
       <c r="K15" t="n">
-        <v>3.0991</v>
+        <v>4.3125</v>
       </c>
       <c r="L15" t="n">
-        <v>2.5027</v>
+        <v>1.3349</v>
       </c>
       <c r="M15" t="n">
-        <v>-2.1234</v>
+        <v>-2.1122</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.17</v>
+        <v>-0.0044</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.9534</v>
+        <v>-2.1078</v>
       </c>
       <c r="P15" t="n">
-        <v>-2.3195</v>
+        <v>0.9278</v>
       </c>
       <c r="Q15" t="n">
-        <v>-3.4793</v>
+        <v>-0.4639</v>
       </c>
       <c r="R15" t="n">
-        <v>1.1598</v>
+        <v>1.3917</v>
       </c>
       <c r="S15" t="n">
-        <v>2.4451</v>
+        <v>-0.0286</v>
       </c>
       <c r="T15" t="n">
-        <v>1.2467</v>
+        <v>0.248</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1984</v>
+        <v>-0.2765</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.1418</v>
+        <v>0.1418</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.1418</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1418</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>N. WILLIAMS-GOSS</t>
+          <t>E. ULANOVAS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.391</v>
+        <v>2.2221</v>
       </c>
       <c r="E16" t="n">
-        <v>4.5117</v>
+        <v>4.5391</v>
       </c>
       <c r="F16" t="n">
-        <v>-1.1207</v>
+        <v>-2.317</v>
       </c>
       <c r="G16" t="n">
-        <v>3.5352</v>
+        <v>1.8926</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3081</v>
+        <v>3.0636</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.7729</v>
+        <v>-1.171</v>
       </c>
       <c r="J16" t="n">
-        <v>5.6474</v>
+        <v>4.3302</v>
       </c>
       <c r="K16" t="n">
-        <v>4.3125</v>
+        <v>3.8651</v>
       </c>
       <c r="L16" t="n">
-        <v>1.3349</v>
+        <v>0.465</v>
       </c>
       <c r="M16" t="n">
-        <v>-2.1122</v>
+        <v>-2.4376</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0044</v>
+        <v>-0.8016</v>
       </c>
       <c r="O16" t="n">
-        <v>-2.1078</v>
+        <v>-1.636</v>
       </c>
       <c r="P16" t="n">
+        <v>-0.6959</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-1.6237</v>
+      </c>
+      <c r="R16" t="n">
         <v>0.9278</v>
       </c>
-      <c r="Q16" t="n">
-        <v>-0.4639</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.3917</v>
-      </c>
       <c r="S16" t="n">
-        <v>-1.2138</v>
+        <v>-0.5829</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.8136</v>
+        <v>0.2243</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4002</v>
+        <v>-0.8072</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="W16" t="n">
-        <v>0.1418</v>
+        <v>1.6083</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>E. ULANOVAS</t>
+          <t>A. TUBELIS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.1054</v>
+        <v>2.0038</v>
       </c>
       <c r="E17" t="n">
-        <v>3.9493</v>
+        <v>2.4257</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.8439</v>
+        <v>-0.4219</v>
       </c>
       <c r="G17" t="n">
-        <v>1.8926</v>
+        <v>3.4784</v>
       </c>
       <c r="H17" t="n">
-        <v>3.0636</v>
+        <v>1.9291</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.171</v>
+        <v>1.5493</v>
       </c>
       <c r="J17" t="n">
-        <v>4.3302</v>
+        <v>5.6018</v>
       </c>
       <c r="K17" t="n">
-        <v>3.8651</v>
+        <v>3.0991</v>
       </c>
       <c r="L17" t="n">
-        <v>0.465</v>
+        <v>2.5027</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.4376</v>
+        <v>-2.1234</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.8016</v>
+        <v>-1.17</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.636</v>
+        <v>-0.9534</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.6959</v>
+        <v>-2.3195</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.6237</v>
+        <v>-3.4793</v>
       </c>
       <c r="R17" t="n">
-        <v>0.9278</v>
+        <v>1.1598</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6996</v>
+        <v>0.9867</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.3655</v>
+        <v>0.3031</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.3341</v>
+        <v>0.6836</v>
       </c>
       <c r="V17" t="n">
-        <v>1.6083</v>
+        <v>-0.1418</v>
       </c>
       <c r="W17" t="n">
-        <v>1.6083</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>M. RUBSTAVICIUS</t>
+          <t>M. LO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1797</v>
+        <v>0.4603</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>0.3578</v>
       </c>
       <c r="F18" t="n">
-        <v>0.1797</v>
+        <v>0.1025</v>
       </c>
       <c r="G18" t="n">
-        <v>0.1573</v>
+        <v>-0.1323</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-1.7718</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1573</v>
+        <v>1.6395</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.5896</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>-2.1574</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>2.7469</v>
       </c>
       <c r="M18" t="n">
-        <v>0.1573</v>
+        <v>-0.7219</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>0.3856</v>
       </c>
       <c r="O18" t="n">
-        <v>0.1573</v>
+        <v>-1.1074</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>0.232</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.4639</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>0.6959</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0224</v>
+        <v>0.3607</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>0.2322</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0224</v>
+        <v>0.1285</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. LO</t>
+          <t>M. RUBSTAVICIUS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.1071</v>
+        <v>0.2133</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2399</v>
+        <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.1327</v>
+        <v>0.2133</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1323</v>
+        <v>0.1573</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7718</v>
+        <v>0</v>
       </c>
       <c r="I19" t="n">
-        <v>1.6395</v>
+        <v>0.1573</v>
       </c>
       <c r="J19" t="n">
-        <v>0.5896</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>-2.1574</v>
+        <v>0</v>
       </c>
       <c r="L19" t="n">
-        <v>2.7469</v>
+        <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.7219</v>
+        <v>0.1573</v>
       </c>
       <c r="N19" t="n">
-        <v>0.3856</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.1074</v>
+        <v>0.1573</v>
       </c>
       <c r="P19" t="n">
-        <v>0.232</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.4639</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>0.6959</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>0.0075</v>
+        <v>0.056</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1142</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.1067</v>
+        <v>0.056</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. WRIGHT</t>
+          <t>D. SLEVA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.8536</v>
+        <v>-0.9199000000000001</v>
       </c>
       <c r="E20" t="n">
-        <v>2.7602</v>
+        <v>0.2518</v>
       </c>
       <c r="F20" t="n">
-        <v>-3.6138</v>
+        <v>-1.1718</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8435</v>
+        <v>-0.0718</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8295</v>
+        <v>-0.0384</v>
       </c>
       <c r="I20" t="n">
-        <v>-1.6729</v>
+        <v>-0.0334</v>
       </c>
       <c r="J20" t="n">
-        <v>1.115</v>
+        <v>0.5427</v>
       </c>
       <c r="K20" t="n">
-        <v>0.8942</v>
+        <v>-0.6351</v>
       </c>
       <c r="L20" t="n">
-        <v>0.2208</v>
+        <v>1.1778</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.9584</v>
+        <v>-0.6143999999999999</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.5967</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.8938</v>
+        <v>-1.2112</v>
       </c>
       <c r="P20" t="n">
-        <v>0.4639</v>
+        <v>0.232</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.232</v>
+        <v>-0.4639</v>
       </c>
       <c r="R20" t="n">
         <v>0.6959</v>
       </c>
       <c r="S20" t="n">
-        <v>2.0647</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="T20" t="n">
-        <v>1.1993</v>
+        <v>0.1731</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8653999999999999</v>
+        <v>-0.181</v>
       </c>
       <c r="V20" t="n">
-        <v>-2.5387</v>
+        <v>-1.0722</v>
       </c>
       <c r="W20" t="n">
-        <v>0.6778999999999999</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.2166</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.0624</v>
+        <v>-0.9616</v>
       </c>
       <c r="E21" t="n">
         <v>-0.9399999999999999</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.1224</v>
+        <v>-0.0216</v>
       </c>
       <c r="G21" t="n">
         <v>-0.591</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.4714</v>
+        <v>-0.3705</v>
       </c>
       <c r="T21" t="n">
         <v>-0.224</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2473</v>
+        <v>-0.1465</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>D. SLEVA</t>
+          <t>M. WRIGHT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.3917</v>
+        <v>-1.9138</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.22</v>
+        <v>2.1704</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.1718</v>
+        <v>-4.0843</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.0718</v>
+        <v>-0.8435</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.0384</v>
+        <v>0.8295</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.0334</v>
+        <v>-1.6729</v>
       </c>
       <c r="J22" t="n">
-        <v>0.5427</v>
+        <v>1.115</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6351</v>
+        <v>0.8942</v>
       </c>
       <c r="L22" t="n">
-        <v>1.1778</v>
+        <v>0.2208</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.6143999999999999</v>
+        <v>-1.9584</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5967</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.2112</v>
+        <v>-1.8938</v>
       </c>
       <c r="P22" t="n">
-        <v>0.232</v>
+        <v>0.4639</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.4639</v>
+        <v>-0.232</v>
       </c>
       <c r="R22" t="n">
         <v>0.6959</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4797</v>
+        <v>1.0045</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.2987</v>
+        <v>0.6095</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.181</v>
+        <v>0.3949</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.0722</v>
+        <v>-2.5387</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>0.6778999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.0722</v>
+        <v>-3.2166</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.4384</v>
+        <v>-3.1524</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.3215</v>
+        <v>-4.2036</v>
       </c>
       <c r="F23" t="n">
-        <v>0.8831</v>
+        <v>1.0512</v>
       </c>
       <c r="G23" t="n">
         <v>-4.7363</v>
@@ -2248,13 +2248,13 @@
         <v>1.1598</v>
       </c>
       <c r="S23" t="n">
-        <v>0.6743</v>
+        <v>0.9603</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.1845</v>
+        <v>-0.06660000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>0.8588</v>
+        <v>1.0269</v>
       </c>
       <c r="V23" t="n">
         <v>-0.5361</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-4.3582</v>
+        <v>-3.4089</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.3275</v>
+        <v>-1.5018</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.0307</v>
+        <v>-1.907</v>
       </c>
       <c r="G24" t="n">
         <v>1.3115</v>
@@ -2326,13 +2326,13 @@
         <v>1.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3711</v>
+        <v>-0.4217</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.187</v>
+        <v>-0.3613</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.1841</v>
+        <v>-0.0604</v>
       </c>
       <c r="V24" t="n">
         <v>2.428</v>
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>2.998700000000001</v>
+        <v>3.784999999999999</v>
       </c>
       <c r="E25" t="n">
         <v>13.587</v>
       </c>
       <c r="F25" t="n">
-        <v>-10.5883</v>
+        <v>-9.802100000000001</v>
       </c>
       <c r="G25" t="n">
-        <v>7.170600000000002</v>
+        <v>7.1706</v>
       </c>
       <c r="H25" t="n">
-        <v>9.027200000000001</v>
+        <v>9.027199999999999</v>
       </c>
       <c r="I25" t="n">
         <v>-1.8565</v>
@@ -2401,19 +2401,19 @@
         <v>-15.077</v>
       </c>
       <c r="R25" t="n">
-        <v>9.278299999999998</v>
+        <v>9.2783</v>
       </c>
       <c r="S25" t="n">
-        <v>1.454</v>
+        <v>2.2406</v>
       </c>
       <c r="T25" t="n">
-        <v>1.5946</v>
+        <v>1.5947</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1405000000000002</v>
+        <v>0.6458999999999999</v>
       </c>
       <c r="V25" t="n">
-        <v>0.1728999999999998</v>
+        <v>0.1729000000000003</v>
       </c>
       <c r="W25" t="n">
         <v>5.4232</v>
